--- a/backend/static/templates/village_import_template.xlsx
+++ b/backend/static/templates/village_import_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="帮扶村数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据导入" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,20 +27,81 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="SimHei"/>
+      <b val="1"/>
+      <color rgb="00d4af37"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="SimHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="SimSun"/>
+      <color rgb="001e293b"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="SimHei"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="14"/>
+      <name val="SimSun"/>
+      <i val="1"/>
+      <color rgb="0064748b"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="SimSun"/>
+      <i val="1"/>
+      <color rgb="0064748b"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="SimSun"/>
+      <color rgb="0064748b"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="SimSun"/>
+      <color rgb="0064748b"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="SimHei"/>
       <b val="1"/>
+      <color rgb="00d4af37"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="SimSun"/>
+      <b val="1"/>
+      <color rgb="0064748b"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="SimSun"/>
+      <b val="1"/>
+      <color rgb="00e63946"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="SimHei"/>
+      <b val="1"/>
+      <color rgb="001b4332"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="SimSun"/>
+      <color rgb="0064748b"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -49,24 +110,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="001b4332"/>
+        <bgColor rgb="001b4332"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00d4af37"/>
+        <bgColor rgb="00d4af37"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00e2efda"/>
+        <bgColor rgb="00e2efda"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e8f0eb"/>
+        <bgColor rgb="00e8f0eb"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -75,36 +148,83 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00cbd5e1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00cbd5e1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00cbd5e1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00cbd5e1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00cbd5e1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00cbd5e1"/>
+      </right>
+      <top style="medium">
+        <color rgb="00d4af37"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00d4af37"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,233 +588,399 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15.4" customWidth="1" min="2" max="2"/>
+    <col width="15.4" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17.6" customWidth="1" min="6" max="6"/>
+    <col width="17.6" customWidth="1" min="7" max="7"/>
+    <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="17.6" customWidth="1" min="9" max="9"/>
+    <col width="41.8" customWidth="1" min="10" max="10"/>
+    <col width="17.6" customWidth="1" min="11" max="11"/>
+    <col width="26.4" customWidth="1" min="12" max="12"/>
+    <col width="17.6" customWidth="1" min="13" max="13"/>
+    <col width="17.6" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="15.4" customWidth="1" min="18" max="18"/>
+    <col width="37.40000000000001" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>★ 军队乡村振兴管理系统 ★</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>帮扶村数据导入模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="3" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>填报单位：____________________    填报人：__________    填报日期：2026年06月07日    年度：__________</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="6" customHeight="1"/>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>*各部门各单位</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>*具体帮扶单位</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>*定点帮扶村</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>地区范围</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>是否属于三区三州</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>是否属于边疆地区</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>是否属于民族地区</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>是否属于革命地区</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>是否属于160个国家乡村振兴重点帮扶县</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>振兴发展梯队系列</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>省级乡村振兴示范创建对象</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>百村示范创建对象</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>梯次振兴发展对象</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>是否跨省</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>是否跨市</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>是否跨大单位协作帮扶</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>是否纳入总盘子</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>2021年以来获得的国家或省级表彰</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>某某部门</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>某某帮扶单位</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>某某村</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>西部地区</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>第一梯队</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>全国先进帮扶村</t>
         </is>
       </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>← 示例行（导入时自动跳过）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="9" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>【填写说明】1. 带 * 为必填字段  2. 日期格式：YYYY-MM-DD  3. 请勿修改表头  4. 单次最多导入1000条</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>— 军队乡村振兴管理系统 v1.3.0 — 2026-06-07 —</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F1001 G2:G1001 H2:H1001 I2:I1001 J2:J1001 L2:L1001 M2:M1001 N2:N1001 O2:O1001 P2:P1001 Q2:Q1001 R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请选择是或否" type="list">
+  <mergeCells count="6">
+    <mergeCell ref="A14:S14"/>
+    <mergeCell ref="A12:S12"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="T7:U7"/>
+  </mergeCells>
+  <dataValidations count="12">
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O8:O1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P8:P1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q8:Q1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入错误" error="请从下拉列表中选择" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.6" right="0.6" top="0.7" bottom="0.7" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -704,513 +990,607 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>帮扶村数据导入模板填写说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>★ 帮扶村数据导入模板 — 填写说明 ★</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="3" customHeight="1">
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>字段名称</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>是否必填</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>数据类型</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>填写说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>整数</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>自动生成的序号</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>各部门各单位</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>★ 必填</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>所属部门名称（必填）</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>具体帮扶单位</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>★ 必填</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>具体帮扶单位名称（必填）</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>定点帮扶村</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>★ 必填</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>帮扶村名称（必填）</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>地区范围</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>所属地区范围</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>是否属于三区三州</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>是否属于边疆地区</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>是否属于民族地区</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>是否属于革命地区</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>是否属于160个国家乡村振兴重点帮扶县</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>振兴发展梯队系列</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>振兴发展梯队</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>省级乡村振兴示范创建对象</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>百村示范创建对象</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>梯次振兴发展对象</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>是否跨省</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>是否跨市</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>是否跨大单位协作帮扶</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>是否纳入总盘子</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>2021年以来获得的国家或省级表彰</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>获得的表彰荣誉</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>注意事项：</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1. 带*号的字段为必填字段，不能为空</t>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>▎注意事项</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2. 是 / 否字段请填写'是'或'否'</t>
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>1. 带 ★ 必填 标记的字段必须填写，否则导入失败</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>3. 单次导入最多支持1000条记录</t>
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>2. 日期字段请使用 YYYY-MM-DD 格式（如 2024-06-15）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>4. 请勿修改表头名称和顺序</t>
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>3. 是 / 否字段请从下拉列表中选择</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>5. 示例数据行（绿色背景）在导入时会被忽略</t>
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>4. 单次导入最多支持 1000 条记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>5. 请勿修改表头名称和列顺序</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>6. 示例数据行（浅绿底色）在导入时自动跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>7. 填写完成后可直接打印（已设定为 A4 纸张大小）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>— 军队乡村振兴管理系统 v1.3.0 —</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A30:D30"/>
+  <mergeCells count="10">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
